--- a/data/bonds/DEBonds10YR.xlsx
+++ b/data/bonds/DEBonds10YR.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GDBR10" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DEbond" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +429,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trade Price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Log_return</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Return</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Z-Score</t>
         </is>
@@ -452,321 +461,602 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2005</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>34699</v>
       </c>
       <c r="C2" t="n">
-        <v>3.379525291828795</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>195.6896</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.8828757631318543</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2006</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>35064</v>
       </c>
       <c r="C3" t="n">
-        <v>3.782788461538462</v>
+        <v>227.5302</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1193</v>
+        <v>1995</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0449638716431962</v>
+        <v>0.1508</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.909625211764133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2007</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>35430</v>
       </c>
       <c r="C4" t="n">
-        <v>4.230214559386975</v>
+        <v>244.1157</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1183</v>
+        <v>1996</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04573075993872647</v>
+        <v>0.0704</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5834759005908466</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2008</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>35795</v>
       </c>
       <c r="C5" t="n">
-        <v>3.99570992366412</v>
+        <v>259.1574</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0554</v>
+        <v>1997</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1789392568723355</v>
+        <v>0.0598</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4086353197645177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2009</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>36160</v>
       </c>
       <c r="C6" t="n">
-        <v>3.266425287356319</v>
+        <v>287.5079</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1825</v>
+        <v>1998</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2764107592342336</v>
+        <v>0.1038</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.134388674137958</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2010</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>36525</v>
       </c>
       <c r="C7" t="n">
-        <v>2.779409961685821</v>
+        <v>281.5192</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1491</v>
+        <v>1999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2507966901635224</v>
+        <v>-0.021</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.9241117491757999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2011</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>36891</v>
       </c>
       <c r="C8" t="n">
-        <v>2.647430769230769</v>
+        <v>302.0883</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0475</v>
+        <v>2000</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1728808393376463</v>
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5851253400326043</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2012</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>37256</v>
       </c>
       <c r="C9" t="n">
-        <v>1.564509578544062</v>
+        <v>318.3836</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.409</v>
+        <v>2001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4501109581718412</v>
+        <v>0.0525</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2882262405161969</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2013</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>37621</v>
       </c>
       <c r="C10" t="n">
-        <v>1.627256704980841</v>
+        <v>347.1897</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0401</v>
+        <v>2002</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1057014246491941</v>
+        <v>0.0866</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8506850901556131</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2014</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>37986</v>
       </c>
       <c r="C11" t="n">
-        <v>1.234693486590039</v>
+        <v>360.2984</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2412</v>
+        <v>2003</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3214271021818608</v>
+        <v>0.0371</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0342125664854929</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2015</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>38352</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5369463601532564</v>
+        <v>386.7502</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5651</v>
+        <v>2004</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5698222211041174</v>
+        <v>0.0708</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5900736583578778</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2016</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>38717</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1368544061302681</v>
+        <v>407.5497</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7451</v>
+        <v>2005</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7078621142995671</v>
+        <v>0.0524</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2865768010744392</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2017</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>39082</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3745038461538464</v>
+        <v>406.0833</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7365</v>
+        <v>2006</v>
       </c>
       <c r="E14" t="n">
-        <v>1.195247879888367</v>
+        <v>-0.0036</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.6371092863099393</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2018</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>39447</v>
       </c>
       <c r="C15" t="n">
-        <v>0.46316091954023</v>
+        <v>414.1784</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2367</v>
+        <v>2007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04506881425205825</v>
+        <v>0.0197</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.2527898963803676</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2019</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>39813</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2102653846153847</v>
+        <v>465.1121</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.454</v>
+        <v>2008</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.25150922700098</v>
+        <v>0.116</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.335620286032412</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2020</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>40178</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4731679389312977</v>
+        <v>474.175</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2503</v>
+        <v>2009</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.095294081201463</v>
+        <v>0.0193</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.2593876541473988</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2021</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>40543</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.3087471264367818</v>
+        <v>503.5763</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3475</v>
+        <v>2010</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1300400373968129</v>
+        <v>0.0602</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.415233077531549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2023</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>40908</v>
       </c>
       <c r="C19" t="n">
-        <v>2.460791505791506</v>
+        <v>551.9389</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0591</v>
+        <v>2011</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6757577484961574</v>
+        <v>0.0917</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.934806501685262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>41274</v>
+      </c>
+      <c r="C20" t="n">
+        <v>576.797</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1496733274085402</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>41639</v>
+      </c>
+      <c r="C21" t="n">
+        <v>563.8967</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.950502780243925</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>42004</v>
+      </c>
+      <c r="C22" t="n">
+        <v>622.1333</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.043669504841278</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>42369</v>
+      </c>
+      <c r="C23" t="n">
+        <v>624.4533</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.5167002070616186</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>42735</v>
+      </c>
+      <c r="C24" t="n">
+        <v>648.9245</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.05565527922834447</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>43100</v>
+      </c>
+      <c r="C25" t="n">
+        <v>640.1581</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.8020532304857213</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>43465</v>
+      </c>
+      <c r="C26" t="n">
+        <v>654.9558</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.2000078342441174</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>43830</v>
+      </c>
+      <c r="C27" t="n">
+        <v>674.7903</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.08619651276282789</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>44196</v>
+      </c>
+      <c r="C28" t="n">
+        <v>694.9807</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.09114483108810137</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="C29" t="n">
+        <v>676.2501</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.028026434006542</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="C30" t="n">
+        <v>586.6377</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3212150293513534</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="C31" t="n">
+        <v>590.3334</v>
+      </c>
+      <c r="D31" t="n">
         <v>2024</v>
       </c>
-      <c r="C20" t="n">
-        <v>2.341833976833973</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-0.0483</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.1734943499740705</v>
+      <c r="E31" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.4738147815759153</v>
       </c>
     </row>
   </sheetData>
